--- a/data/employees.xlsx
+++ b/data/employees.xlsx
@@ -559,7 +559,7 @@
         <v>Kamal qızı</v>
       </c>
       <c r="D3" t="str">
-        <v>17.09.1992</v>
+        <v>18.09.1992</v>
       </c>
       <c r="E3" t="str">
         <v>Mühasibatlıq</v>
@@ -583,7 +583,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
   </ignoredErrors>
